--- a/Rapport_data.xlsx
+++ b/Rapport_data.xlsx
@@ -988,7 +988,16 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="24" t="n"/>
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>NOVOCIB Rapport d'essai 260621-11</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>260621-11</t>
+        </is>
+      </c>
       <c r="C3" s="43" t="n">
         <v>11</v>
       </c>
